--- a/nuclear_attraction_matrix.xlsx
+++ b/nuclear_attraction_matrix.xlsx
@@ -413,21 +413,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M13"/>
+  <dimension ref="A1:AM39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="n">
-        <v>5.068976695109483</v>
+        <v>2.434348400726471</v>
       </c>
       <c r="B1" t="n">
-        <v>9.226357141400744</v>
+        <v>4.174305952720376</v>
       </c>
       <c r="C1" t="n">
-        <v>4.818455861781088</v>
+        <v>2.165715514815903</v>
       </c>
       <c r="D1" t="n">
-        <v>5.001885043864562</v>
+        <v>2.227510585647718</v>
       </c>
       <c r="E1" t="n">
         <v>0</v>
@@ -436,7 +436,7 @@
         <v>0</v>
       </c>
       <c r="G1" t="n">
-        <v>0</v>
+        <v>0.03612803534483119</v>
       </c>
       <c r="H1" t="n">
         <v>0</v>
@@ -445,7 +445,7 @@
         <v>0</v>
       </c>
       <c r="J1" t="n">
-        <v>0</v>
+        <v>0.03074431601516749</v>
       </c>
       <c r="K1" t="n">
         <v>0</v>
@@ -454,21 +454,99 @@
         <v>0</v>
       </c>
       <c r="M1" t="n">
-        <v>0</v>
+        <v>0.03310305217715039</v>
+      </c>
+      <c r="N1" t="n">
+        <v>1.307264394918665e-07</v>
+      </c>
+      <c r="O1" t="n">
+        <v>0.01743039107990151</v>
+      </c>
+      <c r="P1" t="n">
+        <v>0.5431867054195724</v>
+      </c>
+      <c r="Q1" t="n">
+        <v>1.429287260010326</v>
+      </c>
+      <c r="R1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S1" t="n">
+        <v>0</v>
+      </c>
+      <c r="T1" t="n">
+        <v>-0.01243256009909264</v>
+      </c>
+      <c r="U1" t="n">
+        <v>0</v>
+      </c>
+      <c r="V1" t="n">
+        <v>0</v>
+      </c>
+      <c r="W1" t="n">
+        <v>-0.4022529021585955</v>
+      </c>
+      <c r="X1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z1" t="n">
+        <v>-1.078181578774176</v>
+      </c>
+      <c r="AA1" t="n">
+        <v>0.07541417021504283</v>
+      </c>
+      <c r="AB1" t="n">
+        <v>1.334317960504578</v>
+      </c>
+      <c r="AC1" t="n">
+        <v>1.771519152688794</v>
+      </c>
+      <c r="AD1" t="n">
+        <v>2.117293682029547</v>
+      </c>
+      <c r="AE1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG1" t="n">
+        <v>-0.4667975930779076</v>
+      </c>
+      <c r="AH1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ1" t="n">
+        <v>-0.6526631423438809</v>
+      </c>
+      <c r="AK1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM1" t="n">
+        <v>-0.7851293796347598</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>9.226357141400744</v>
+        <v>4.174305952720376</v>
       </c>
       <c r="B2" t="n">
-        <v>32.22876908496174</v>
+        <v>13.06052722654094</v>
       </c>
       <c r="C2" t="n">
-        <v>32.29937616114243</v>
+        <v>12.92596364211132</v>
       </c>
       <c r="D2" t="n">
-        <v>40.05852661379053</v>
+        <v>15.21926130681365</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -477,7 +555,7 @@
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>0.5819261365744327</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -486,7 +564,7 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>1.475462685247074</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -495,21 +573,99 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>2.723285606951114</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.01743039107990151</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.490231622028156</v>
+      </c>
+      <c r="P2" t="n">
+        <v>4.845510914791227</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>10.58662948285118</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>-0.2061440175606415</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W2" t="n">
+        <v>-2.557666263640906</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>-6.783031577562518</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.485963741094274</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>9.909621808159049</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>12.19069638500658</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>15.20035014125642</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>-1.920103295587711</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>-2.937951817427892</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>-3.920084758666563</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>4.818455861781088</v>
+        <v>2.165715514815903</v>
       </c>
       <c r="B3" t="n">
-        <v>32.29937616114243</v>
+        <v>12.92596364211132</v>
       </c>
       <c r="C3" t="n">
-        <v>55.86229505209933</v>
+        <v>29.78012778499279</v>
       </c>
       <c r="D3" t="n">
-        <v>88.69774935427792</v>
+        <v>46.81865315370642</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -518,7 +674,7 @@
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>1.475462685247074</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -527,7 +683,7 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>6.912828115024684</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -536,21 +692,99 @@
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>13.76609940898933</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.5431867054195724</v>
+      </c>
+      <c r="O3" t="n">
+        <v>4.845510914791227</v>
+      </c>
+      <c r="P3" t="n">
+        <v>17.32415064143466</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>35.62818789497686</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>-0.8699643340567231</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W3" t="n">
+        <v>-6.386771320030403</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>-14.56002376289724</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>3.336305772443246</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>21.16426246201538</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>33.80057812087689</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>52.01707348256272</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>-1.58360051486611</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>-1.931230738473717</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>-0.9083798727691463</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>5.001885043864562</v>
+        <v>2.227510585647718</v>
       </c>
       <c r="B4" t="n">
-        <v>40.05852661379053</v>
+        <v>15.21926130681365</v>
       </c>
       <c r="C4" t="n">
-        <v>88.69774935427792</v>
+        <v>46.81865315370642</v>
       </c>
       <c r="D4" t="n">
-        <v>215.1775790129995</v>
+        <v>108.903938367716</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -559,7 +793,7 @@
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>2.723285606951114</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -568,7 +802,7 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>13.76609940898933</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -577,7 +811,85 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>43.12718909070011</v>
+      </c>
+      <c r="N4" t="n">
+        <v>1.429287260010326</v>
+      </c>
+      <c r="O4" t="n">
+        <v>10.58662948285118</v>
+      </c>
+      <c r="P4" t="n">
+        <v>35.62818789497686</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>88.84910835348506</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>-1.951915814274622</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W4" t="n">
+        <v>-14.54647111698702</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>-33.16862483265336</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>4.420951055493485</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>33.91433881676754</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>72.19263602079079</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>141.3241977126706</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>-0.1249674833846785</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>0.3025663064397889</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>1.081909292108518</v>
       </c>
     </row>
     <row r="5">
@@ -594,7 +906,7 @@
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>1.137378908278753</v>
+        <v>0.2853972197103467</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
@@ -603,7 +915,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>1.950322358850911</v>
+        <v>0.5704004591766563</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -612,12 +924,90 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>2.898755278118104</v>
+        <v>0.7431625285019476</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
       </c>
       <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0.01563841608151445</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0.1725677294452</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0.4838632495674671</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0.2622024283349141</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0.5214165634387384</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>0.7487048722039288</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -638,7 +1028,7 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>1.137378908278753</v>
+        <v>0.2853972197103467</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -647,7 +1037,7 @@
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>1.950322358850911</v>
+        <v>0.5704004591766563</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -656,24 +1046,102 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>2.898755278118104</v>
+        <v>0.7431625285019476</v>
       </c>
       <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0.01563841608151445</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0.1725677294452</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0.4838632495674671</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0.2622024283349141</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>0.5214165634387384</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>0.7487048722039288</v>
+      </c>
+      <c r="AM6" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>0</v>
+        <v>0.03612803534483119</v>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
+        <v>0.5819261365744327</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>1.475462685247074</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>2.723285606951114</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -682,7 +1150,7 @@
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>4.787868901930422</v>
+        <v>0.5711015356669351</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -691,7 +1159,7 @@
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>7.131155313768676</v>
+        <v>2.053669168999045</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -700,7 +1168,85 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>9.194165537090267</v>
+        <v>2.555265362533367</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.01243256009909264</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.2061440175606415</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0.8699643340567231</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1.951915814274622</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>-0.1462491113952548</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" t="n">
+        <v>-0.6352935113571994</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>-0.8450103837543532</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0.4733196961457358</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1.968478664875505</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>2.226424481524636</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>2.767195353540904</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0.08398795187986882</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>0.4842143590045994</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>0.8854245365213008</v>
       </c>
     </row>
     <row r="8">
@@ -717,7 +1263,7 @@
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>1.950322358850911</v>
+        <v>0.5704004591766563</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -726,7 +1272,7 @@
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>9.075479995174197</v>
+        <v>3.16154127556073</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -735,12 +1281,90 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>24.62064838514615</v>
+        <v>8.214014097789462</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
       </c>
       <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0.1725677294452</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.542054538569412</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" t="n">
+        <v>5.603764269656633</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1.364406061941381</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>4.505430107075472</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>9.522490492366085</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -761,7 +1385,7 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>1.950322358850911</v>
+        <v>0.5704004591766563</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -770,7 +1394,7 @@
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>9.075479995174197</v>
+        <v>3.16154127556073</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -779,24 +1403,102 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>24.62064838514615</v>
+        <v>8.214014097789462</v>
       </c>
       <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0.1725677294452</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.542054538569412</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>5.603764269656633</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>1.364406061941381</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>4.505430107075472</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>9.522490492366085</v>
+      </c>
+      <c r="AM9" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>0</v>
+        <v>0.03074431601516749</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>1.475462685247074</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>6.912828115024684</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>13.76609940898933</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -805,7 +1507,7 @@
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>7.131155313768676</v>
+        <v>2.053669168999045</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -814,7 +1516,7 @@
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>19.09792055812151</v>
+        <v>9.182915884386372</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
@@ -823,7 +1525,85 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>40.53420725596166</v>
+        <v>32.06314043183138</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.4022529021585955</v>
+      </c>
+      <c r="O10" t="n">
+        <v>2.557666263640906</v>
+      </c>
+      <c r="P10" t="n">
+        <v>6.386771320030403</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>14.54647111698702</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>-0.6352935113571994</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" t="n">
+        <v>-1.52926017435174</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>0.4694291144653469</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.238677130179292</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>6.813859831549175</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>11.80075323133549</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>22.22503194992464</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>4.242528199249179</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>10.4610668701075</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>20.7185039967505</v>
       </c>
     </row>
     <row r="11">
@@ -840,7 +1620,7 @@
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>2.898755278118104</v>
+        <v>0.7431625285019476</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
@@ -849,7 +1629,7 @@
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>24.62064838514615</v>
+        <v>8.214014097789462</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -858,12 +1638,90 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>155.9418841040438</v>
+        <v>35.43540225019624</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
       </c>
       <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0.4838632495674671</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" t="n">
+        <v>5.603764269656633</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" t="n">
+        <v>31.82421684985162</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>2.357252238529592</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>15.41053232778258</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>65.23649142050101</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM11" t="n">
         <v>0</v>
       </c>
     </row>
@@ -884,7 +1742,7 @@
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>2.898755278118104</v>
+        <v>0.7431625285019476</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -893,7 +1751,7 @@
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>24.62064838514615</v>
+        <v>8.214014097789462</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -902,24 +1760,102 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>155.9418841040438</v>
+        <v>35.43540225019624</v>
       </c>
       <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0.4838632495674671</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" t="n">
+        <v>5.603764269656633</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>31.82421684985162</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>2.357252238529592</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>15.41053232778258</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>65.23649142050101</v>
+      </c>
+      <c r="AM12" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>0</v>
+        <v>0.03310305217715039</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2.723285606951114</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>13.76609940898933</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>43.12718909070011</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -928,24 +1864,3196 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
+        <v>2.555265362533367</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>32.06314043183138</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>85.46294159540837</v>
+      </c>
+      <c r="N13" t="n">
+        <v>1.078181578774176</v>
+      </c>
+      <c r="O13" t="n">
+        <v>6.783031577562518</v>
+      </c>
+      <c r="P13" t="n">
+        <v>14.56002376289724</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>33.16862483265336</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>-0.8450103837543532</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0.4694291144653469</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>11.17217963092373</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.699289029572803</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>13.31609014834212</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>26.07967493010795</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>54.08455612943948</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>7.152493786127149</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>25.40109815048218</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>87.56786229511877</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>1.307264394918665e-07</v>
+      </c>
+      <c r="B14" t="n">
+        <v>0.01743039107990151</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.5431867054195724</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1.429287260010326</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.01243256009909264</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.4022529021585955</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1.078181578774176</v>
+      </c>
+      <c r="N14" t="n">
+        <v>2.434348400726471</v>
+      </c>
+      <c r="O14" t="n">
+        <v>4.174305952720376</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2.165715514815903</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>2.227510585647718</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>-0.03612803534483119</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" t="n">
+        <v>-0.03074431601516749</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>-0.03310305217715039</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>0.07541417021504283</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.334317960504578</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1.771519152688794</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>2.117293682029547</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>0.4667975930779076</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>0.6526631423438809</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>0.7851293796347598</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>0.01743039107990151</v>
+      </c>
+      <c r="B15" t="n">
+        <v>0.490231622028156</v>
+      </c>
+      <c r="C15" t="n">
+        <v>4.845510914791227</v>
+      </c>
+      <c r="D15" t="n">
+        <v>10.58662948285118</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.2061440175606415</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>2.557666263640906</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>6.783031577562518</v>
+      </c>
+      <c r="N15" t="n">
+        <v>4.174305952720376</v>
+      </c>
+      <c r="O15" t="n">
+        <v>13.06052722654094</v>
+      </c>
+      <c r="P15" t="n">
+        <v>12.92596364211132</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>15.21926130681365</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>-0.5819261365744327</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" t="n">
+        <v>-1.475462685247074</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>-2.723285606951114</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.485963741094274</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>9.909621808159049</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>12.19069638500658</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>15.20035014125642</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>1.920103295587711</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>2.937951817427892</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>3.920084758666563</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>0.5431867054195724</v>
+      </c>
+      <c r="B16" t="n">
+        <v>4.845510914791227</v>
+      </c>
+      <c r="C16" t="n">
+        <v>17.32415064143466</v>
+      </c>
+      <c r="D16" t="n">
+        <v>35.62818789497686</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.8699643340567231</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>6.386771320030403</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>14.56002376289724</v>
+      </c>
+      <c r="N16" t="n">
+        <v>2.165715514815903</v>
+      </c>
+      <c r="O16" t="n">
+        <v>12.92596364211132</v>
+      </c>
+      <c r="P16" t="n">
+        <v>29.78012778499279</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>46.81865315370642</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>-1.475462685247074</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" t="n">
+        <v>-6.912828115024684</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>-13.76609940898933</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>3.336305772443246</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>21.16426246201538</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>33.80057812087689</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>52.01707348256272</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>1.58360051486611</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>1.931230738473717</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>0.9083798727691463</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>1.429287260010326</v>
+      </c>
+      <c r="B17" t="n">
+        <v>10.58662948285118</v>
+      </c>
+      <c r="C17" t="n">
+        <v>35.62818789497686</v>
+      </c>
+      <c r="D17" t="n">
+        <v>88.84910835348506</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>1.951915814274622</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
+        <v>14.54647111698702</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>33.16862483265336</v>
+      </c>
+      <c r="N17" t="n">
+        <v>2.227510585647718</v>
+      </c>
+      <c r="O17" t="n">
+        <v>15.21926130681365</v>
+      </c>
+      <c r="P17" t="n">
+        <v>46.81865315370642</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>108.903938367716</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>-2.723285606951114</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0</v>
+      </c>
+      <c r="W17" t="n">
+        <v>-13.76609940898933</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>-43.12718909070011</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>4.420951055493485</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>33.91433881676754</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>72.19263602079079</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>141.3241977126706</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>0.1249674833846785</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>-0.3025663064397889</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>-1.081909292108518</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>0</v>
+      </c>
+      <c r="B18" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.01563841608151445</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.1725677294452</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0.4838632495674671</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0.2853972197103467</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0.5704004591766563</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0</v>
+      </c>
+      <c r="X18" t="n">
+        <v>0.7431625285019476</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>0.2622024283349141</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>0.5214165634387384</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>0.7487048722039288</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>0</v>
+      </c>
+      <c r="B19" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.01563841608151445</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.1725677294452</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0.4838632495674671</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0.2853972197103467</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0.5704004591766563</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0</v>
+      </c>
+      <c r="X19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>0.7431625285019476</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>0.2622024283349141</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>0.5214165634387384</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>0.7487048722039288</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>-0.01243256009909264</v>
+      </c>
+      <c r="B20" t="n">
+        <v>-0.2061440175606415</v>
+      </c>
+      <c r="C20" t="n">
+        <v>-0.8699643340567231</v>
+      </c>
+      <c r="D20" t="n">
+        <v>-1.951915814274622</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-0.1462491113952548</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="n">
+        <v>-0.6352935113571994</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>-0.8450103837543532</v>
+      </c>
+      <c r="N20" t="n">
+        <v>-0.03612803534483119</v>
+      </c>
+      <c r="O20" t="n">
+        <v>-0.5819261365744327</v>
+      </c>
+      <c r="P20" t="n">
+        <v>-1.475462685247074</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>-2.723285606951114</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0.5711015356669351</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" t="n">
+        <v>0</v>
+      </c>
+      <c r="W20" t="n">
+        <v>2.053669168999045</v>
+      </c>
+      <c r="X20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>2.555265362533367</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>-0.4733196961457358</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>-1.968478664875505</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>-2.226424481524636</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>-2.767195353540904</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>0.08398795187986882</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>0.4842143590045994</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>0.8854245365213008</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>0</v>
+      </c>
+      <c r="B21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.1725677294452</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1.542054538569412</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>5.603764269656633</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0.5704004591766563</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0</v>
+      </c>
+      <c r="U21" t="n">
+        <v>3.16154127556073</v>
+      </c>
+      <c r="V21" t="n">
+        <v>0</v>
+      </c>
+      <c r="W21" t="n">
+        <v>0</v>
+      </c>
+      <c r="X21" t="n">
+        <v>8.214014097789462</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1.364406061941381</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>4.505430107075472</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>9.522490492366085</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>0</v>
+      </c>
+      <c r="B22" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.1725677294452</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="n">
+        <v>1.542054538569412</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>5.603764269656633</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0.5704004591766563</v>
+      </c>
+      <c r="T22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" t="n">
+        <v>3.16154127556073</v>
+      </c>
+      <c r="W22" t="n">
+        <v>0</v>
+      </c>
+      <c r="X22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>8.214014097789462</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>1.364406061941381</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>4.505430107075472</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>9.522490492366085</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>-0.4022529021585955</v>
+      </c>
+      <c r="B23" t="n">
+        <v>-2.557666263640906</v>
+      </c>
+      <c r="C23" t="n">
+        <v>-6.386771320030403</v>
+      </c>
+      <c r="D23" t="n">
+        <v>-14.54647111698702</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-0.6352935113571994</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" t="n">
+        <v>-1.52926017435174</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0.4694291144653469</v>
+      </c>
+      <c r="N23" t="n">
+        <v>-0.03074431601516749</v>
+      </c>
+      <c r="O23" t="n">
+        <v>-1.475462685247074</v>
+      </c>
+      <c r="P23" t="n">
+        <v>-6.912828115024684</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>-13.76609940898933</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2.053669168999045</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" t="n">
+        <v>0</v>
+      </c>
+      <c r="W23" t="n">
+        <v>9.182915884386372</v>
+      </c>
+      <c r="X23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>32.06314043183138</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>-1.238677130179292</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>-6.813859831549175</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>-11.80075323133549</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>-22.22503194992464</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>4.242528199249179</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>10.4610668701075</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>20.7185039967505</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>0</v>
+      </c>
+      <c r="B24" t="n">
+        <v>0</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.4838632495674671</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" t="n">
+        <v>5.603764269656633</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
+        <v>31.82421684985162</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>0</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0.7431625285019476</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>0</v>
+      </c>
+      <c r="U24" t="n">
+        <v>8.214014097789462</v>
+      </c>
+      <c r="V24" t="n">
+        <v>0</v>
+      </c>
+      <c r="W24" t="n">
+        <v>0</v>
+      </c>
+      <c r="X24" t="n">
+        <v>35.43540225019624</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>2.357252238529592</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>15.41053232778258</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>65.23649142050101</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>0</v>
+      </c>
+      <c r="B25" t="n">
+        <v>0</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0.4838632495674671</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="n">
+        <v>5.603764269656633</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
+        <v>31.82421684985162</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0.7431625285019476</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
+      </c>
+      <c r="V25" t="n">
+        <v>8.214014097789462</v>
+      </c>
+      <c r="W25" t="n">
+        <v>0</v>
+      </c>
+      <c r="X25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>35.43540225019624</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>2.357252238529592</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>15.41053232778258</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>65.23649142050101</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>-1.078181578774176</v>
+      </c>
+      <c r="B26" t="n">
+        <v>-6.783031577562518</v>
+      </c>
+      <c r="C26" t="n">
+        <v>-14.56002376289724</v>
+      </c>
+      <c r="D26" t="n">
+        <v>-33.16862483265336</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-0.8450103837543532</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0.4694291144653469</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
+        <v>11.17217963092373</v>
+      </c>
+      <c r="N26" t="n">
+        <v>-0.03310305217715039</v>
+      </c>
+      <c r="O26" t="n">
+        <v>-2.723285606951114</v>
+      </c>
+      <c r="P26" t="n">
+        <v>-13.76609940898933</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>-43.12718909070011</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" t="n">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2.555265362533367</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
+      </c>
+      <c r="V26" t="n">
+        <v>0</v>
+      </c>
+      <c r="W26" t="n">
+        <v>32.06314043183138</v>
+      </c>
+      <c r="X26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>85.46294159540837</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>-1.699289029572803</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>-13.31609014834212</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>-26.07967493010795</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>-54.08455612943948</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>7.152493786127149</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>25.40109815048218</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>87.56786229511877</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>0.07541417021504283</v>
+      </c>
+      <c r="B27" t="n">
+        <v>1.485963741094274</v>
+      </c>
+      <c r="C27" t="n">
+        <v>3.336305772443246</v>
+      </c>
+      <c r="D27" t="n">
+        <v>4.420951055493485</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0.4733196961457358</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" t="n">
+        <v>1.238677130179292</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
+        <v>1.699289029572803</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0.07541417021504283</v>
+      </c>
+      <c r="O27" t="n">
+        <v>1.485963741094274</v>
+      </c>
+      <c r="P27" t="n">
+        <v>3.336305772443246</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>4.420951055493485</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" t="n">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>-0.4733196961457358</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
+      </c>
+      <c r="V27" t="n">
+        <v>0</v>
+      </c>
+      <c r="W27" t="n">
+        <v>-1.238677130179292</v>
+      </c>
+      <c r="X27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>-1.699289029572803</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>5.068976695109483</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>9.226357141400744</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>4.818455861781088</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>5.001885043864562</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>1.334317960504578</v>
+      </c>
+      <c r="B28" t="n">
+        <v>9.909621808159049</v>
+      </c>
+      <c r="C28" t="n">
+        <v>21.16426246201538</v>
+      </c>
+      <c r="D28" t="n">
+        <v>33.91433881676754</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" t="n">
+        <v>1.968478664875505</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" t="n">
+        <v>6.813859831549175</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
+        <v>13.31609014834212</v>
+      </c>
+      <c r="N28" t="n">
+        <v>1.334317960504578</v>
+      </c>
+      <c r="O28" t="n">
+        <v>9.909621808159049</v>
+      </c>
+      <c r="P28" t="n">
+        <v>21.16426246201538</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>33.91433881676754</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" t="n">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>-1.968478664875505</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
+      </c>
+      <c r="V28" t="n">
+        <v>0</v>
+      </c>
+      <c r="W28" t="n">
+        <v>-6.813859831549175</v>
+      </c>
+      <c r="X28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>-13.31609014834212</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>9.226357141400744</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>32.22876908496174</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>32.29937616114243</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>40.05852661379053</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>1.771519152688794</v>
+      </c>
+      <c r="B29" t="n">
+        <v>12.19069638500658</v>
+      </c>
+      <c r="C29" t="n">
+        <v>33.80057812087689</v>
+      </c>
+      <c r="D29" t="n">
+        <v>72.19263602079079</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" t="n">
+        <v>2.226424481524636</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" t="n">
+        <v>11.80075323133549</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
+        <v>26.07967493010795</v>
+      </c>
+      <c r="N29" t="n">
+        <v>1.771519152688794</v>
+      </c>
+      <c r="O29" t="n">
+        <v>12.19069638500658</v>
+      </c>
+      <c r="P29" t="n">
+        <v>33.80057812087689</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>72.19263602079079</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0</v>
+      </c>
+      <c r="S29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>-2.226424481524636</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
+      </c>
+      <c r="V29" t="n">
+        <v>0</v>
+      </c>
+      <c r="W29" t="n">
+        <v>-11.80075323133549</v>
+      </c>
+      <c r="X29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>-26.07967493010795</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>4.818455861781088</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>32.29937616114243</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>55.86229505209933</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>88.69774935427792</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>2.117293682029547</v>
+      </c>
+      <c r="B30" t="n">
+        <v>15.20035014125642</v>
+      </c>
+      <c r="C30" t="n">
+        <v>52.01707348256272</v>
+      </c>
+      <c r="D30" t="n">
+        <v>141.3241977126706</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" t="n">
+        <v>2.767195353540904</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" t="n">
+        <v>22.22503194992464</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" t="n">
+        <v>54.08455612943948</v>
+      </c>
+      <c r="N30" t="n">
+        <v>2.117293682029547</v>
+      </c>
+      <c r="O30" t="n">
+        <v>15.20035014125642</v>
+      </c>
+      <c r="P30" t="n">
+        <v>52.01707348256272</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>141.3241977126706</v>
+      </c>
+      <c r="R30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" t="n">
+        <v>0</v>
+      </c>
+      <c r="T30" t="n">
+        <v>-2.767195353540904</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0</v>
+      </c>
+      <c r="V30" t="n">
+        <v>0</v>
+      </c>
+      <c r="W30" t="n">
+        <v>-22.22503194992464</v>
+      </c>
+      <c r="X30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>-54.08455612943948</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>5.001885043864562</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>40.05852661379053</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>88.69774935427792</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>215.1775790129995</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>0</v>
+      </c>
+      <c r="B31" t="n">
+        <v>0</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.2622024283349141</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" t="n">
+        <v>1.364406061941381</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" t="n">
+        <v>2.357252238529592</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>0</v>
+      </c>
+      <c r="R31" t="n">
+        <v>0.2622024283349141</v>
+      </c>
+      <c r="S31" t="n">
+        <v>0</v>
+      </c>
+      <c r="T31" t="n">
+        <v>0</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1.364406061941381</v>
+      </c>
+      <c r="V31" t="n">
+        <v>0</v>
+      </c>
+      <c r="W31" t="n">
+        <v>0</v>
+      </c>
+      <c r="X31" t="n">
+        <v>2.357252238529592</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>1.137378908278753</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>1.950322358850911</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>2.898755278118104</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>0</v>
+      </c>
+      <c r="B32" t="n">
+        <v>0</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0.2622024283349141</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" t="n">
+        <v>1.364406061941381</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" t="n">
+        <v>2.357252238529592</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>0</v>
+      </c>
+      <c r="R32" t="n">
+        <v>0</v>
+      </c>
+      <c r="S32" t="n">
+        <v>0.2622024283349141</v>
+      </c>
+      <c r="T32" t="n">
+        <v>0</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0</v>
+      </c>
+      <c r="V32" t="n">
+        <v>1.364406061941381</v>
+      </c>
+      <c r="W32" t="n">
+        <v>0</v>
+      </c>
+      <c r="X32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>2.357252238529592</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>1.137378908278753</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>1.950322358850911</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>2.898755278118104</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>-0.4667975930779076</v>
+      </c>
+      <c r="B33" t="n">
+        <v>-1.920103295587711</v>
+      </c>
+      <c r="C33" t="n">
+        <v>-1.58360051486611</v>
+      </c>
+      <c r="D33" t="n">
+        <v>-0.1249674833846785</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0.08398795187986882</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" t="n">
+        <v>4.242528199249179</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" t="n">
+        <v>7.152493786127149</v>
+      </c>
+      <c r="N33" t="n">
+        <v>0.4667975930779076</v>
+      </c>
+      <c r="O33" t="n">
+        <v>1.920103295587711</v>
+      </c>
+      <c r="P33" t="n">
+        <v>1.58360051486611</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>0.1249674833846785</v>
+      </c>
+      <c r="R33" t="n">
+        <v>0</v>
+      </c>
+      <c r="S33" t="n">
+        <v>0</v>
+      </c>
+      <c r="T33" t="n">
+        <v>0.08398795187986882</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0</v>
+      </c>
+      <c r="V33" t="n">
+        <v>0</v>
+      </c>
+      <c r="W33" t="n">
+        <v>4.242528199249179</v>
+      </c>
+      <c r="X33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>7.152493786127149</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>4.787868901930422</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>7.131155313768676</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM33" t="n">
         <v>9.194165537090267</v>
       </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" t="n">
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>0</v>
+      </c>
+      <c r="B34" t="n">
+        <v>0</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0</v>
+      </c>
+      <c r="D34" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.5214165634387384</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" t="n">
+        <v>4.505430107075472</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" t="n">
+        <v>15.41053232778258</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>0</v>
+      </c>
+      <c r="R34" t="n">
+        <v>0.5214165634387384</v>
+      </c>
+      <c r="S34" t="n">
+        <v>0</v>
+      </c>
+      <c r="T34" t="n">
+        <v>0</v>
+      </c>
+      <c r="U34" t="n">
+        <v>4.505430107075472</v>
+      </c>
+      <c r="V34" t="n">
+        <v>0</v>
+      </c>
+      <c r="W34" t="n">
+        <v>0</v>
+      </c>
+      <c r="X34" t="n">
+        <v>15.41053232778258</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>1.950322358850911</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>9.075479995174197</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>24.62064838514615</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM34" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>0</v>
+      </c>
+      <c r="B35" t="n">
+        <v>0</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0</v>
+      </c>
+      <c r="D35" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0.5214165634387384</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" t="n">
+        <v>4.505430107075472</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" t="n">
+        <v>15.41053232778258</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>0</v>
+      </c>
+      <c r="R35" t="n">
+        <v>0</v>
+      </c>
+      <c r="S35" t="n">
+        <v>0.5214165634387384</v>
+      </c>
+      <c r="T35" t="n">
+        <v>0</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0</v>
+      </c>
+      <c r="V35" t="n">
+        <v>4.505430107075472</v>
+      </c>
+      <c r="W35" t="n">
+        <v>0</v>
+      </c>
+      <c r="X35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>15.41053232778258</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>1.950322358850911</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>9.075479995174197</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL35" t="n">
+        <v>24.62064838514615</v>
+      </c>
+      <c r="AM35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>-0.6526631423438809</v>
+      </c>
+      <c r="B36" t="n">
+        <v>-2.937951817427892</v>
+      </c>
+      <c r="C36" t="n">
+        <v>-1.931230738473717</v>
+      </c>
+      <c r="D36" t="n">
+        <v>0.3025663064397889</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0.4842143590045994</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" t="n">
+        <v>10.4610668701075</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" t="n">
+        <v>25.40109815048218</v>
+      </c>
+      <c r="N36" t="n">
+        <v>0.6526631423438809</v>
+      </c>
+      <c r="O36" t="n">
+        <v>2.937951817427892</v>
+      </c>
+      <c r="P36" t="n">
+        <v>1.931230738473717</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>-0.3025663064397889</v>
+      </c>
+      <c r="R36" t="n">
+        <v>0</v>
+      </c>
+      <c r="S36" t="n">
+        <v>0</v>
+      </c>
+      <c r="T36" t="n">
+        <v>0.4842143590045994</v>
+      </c>
+      <c r="U36" t="n">
+        <v>0</v>
+      </c>
+      <c r="V36" t="n">
+        <v>0</v>
+      </c>
+      <c r="W36" t="n">
+        <v>10.4610668701075</v>
+      </c>
+      <c r="X36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>25.40109815048218</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>7.131155313768676</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ36" t="n">
+        <v>19.09792055812151</v>
+      </c>
+      <c r="AK36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM36" t="n">
         <v>40.53420725596166</v>
       </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" t="n">
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>0</v>
+      </c>
+      <c r="B37" t="n">
+        <v>0</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0</v>
+      </c>
+      <c r="D37" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.7487048722039288</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" t="n">
+        <v>9.522490492366085</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" t="n">
+        <v>65.23649142050101</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" t="n">
+        <v>0</v>
+      </c>
+      <c r="N37" t="n">
+        <v>0</v>
+      </c>
+      <c r="O37" t="n">
+        <v>0</v>
+      </c>
+      <c r="P37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>0</v>
+      </c>
+      <c r="R37" t="n">
+        <v>0.7487048722039288</v>
+      </c>
+      <c r="S37" t="n">
+        <v>0</v>
+      </c>
+      <c r="T37" t="n">
+        <v>0</v>
+      </c>
+      <c r="U37" t="n">
+        <v>9.522490492366085</v>
+      </c>
+      <c r="V37" t="n">
+        <v>0</v>
+      </c>
+      <c r="W37" t="n">
+        <v>0</v>
+      </c>
+      <c r="X37" t="n">
+        <v>65.23649142050101</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>2.898755278118104</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>24.62064838514615</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK37" t="n">
+        <v>155.9418841040438</v>
+      </c>
+      <c r="AL37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM37" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>0</v>
+      </c>
+      <c r="B38" t="n">
+        <v>0</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0</v>
+      </c>
+      <c r="D38" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0.7487048722039288</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" t="n">
+        <v>9.522490492366085</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" t="n">
+        <v>65.23649142050101</v>
+      </c>
+      <c r="M38" t="n">
+        <v>0</v>
+      </c>
+      <c r="N38" t="n">
+        <v>0</v>
+      </c>
+      <c r="O38" t="n">
+        <v>0</v>
+      </c>
+      <c r="P38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>0</v>
+      </c>
+      <c r="R38" t="n">
+        <v>0</v>
+      </c>
+      <c r="S38" t="n">
+        <v>0.7487048722039288</v>
+      </c>
+      <c r="T38" t="n">
+        <v>0</v>
+      </c>
+      <c r="U38" t="n">
+        <v>0</v>
+      </c>
+      <c r="V38" t="n">
+        <v>9.522490492366085</v>
+      </c>
+      <c r="W38" t="n">
+        <v>0</v>
+      </c>
+      <c r="X38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>65.23649142050101</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>2.898755278118104</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI38" t="n">
+        <v>24.62064838514615</v>
+      </c>
+      <c r="AJ38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL38" t="n">
+        <v>155.9418841040438</v>
+      </c>
+      <c r="AM38" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>-0.7851293796347598</v>
+      </c>
+      <c r="B39" t="n">
+        <v>-3.920084758666563</v>
+      </c>
+      <c r="C39" t="n">
+        <v>-0.9083798727691463</v>
+      </c>
+      <c r="D39" t="n">
+        <v>1.081909292108518</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0.8854245365213008</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" t="n">
+        <v>20.7185039967505</v>
+      </c>
+      <c r="K39" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" t="n">
+        <v>87.56786229511877</v>
+      </c>
+      <c r="N39" t="n">
+        <v>0.7851293796347598</v>
+      </c>
+      <c r="O39" t="n">
+        <v>3.920084758666563</v>
+      </c>
+      <c r="P39" t="n">
+        <v>0.9083798727691463</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>-1.081909292108518</v>
+      </c>
+      <c r="R39" t="n">
+        <v>0</v>
+      </c>
+      <c r="S39" t="n">
+        <v>0</v>
+      </c>
+      <c r="T39" t="n">
+        <v>0.8854245365213008</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0</v>
+      </c>
+      <c r="V39" t="n">
+        <v>0</v>
+      </c>
+      <c r="W39" t="n">
+        <v>20.7185039967505</v>
+      </c>
+      <c r="X39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>87.56786229511877</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>9.194165537090267</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ39" t="n">
+        <v>40.53420725596166</v>
+      </c>
+      <c r="AK39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM39" t="n">
         <v>194.5476108133628</v>
       </c>
     </row>

--- a/nuclear_attraction_matrix.xlsx
+++ b/nuclear_attraction_matrix.xlsx
@@ -418,13 +418,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="n">
-        <v>-66.0430810802811</v>
+        <v>-66.04308107565103</v>
       </c>
       <c r="B1" t="n">
-        <v>-5.989904541595686</v>
+        <v>-5.98990454337081</v>
       </c>
       <c r="C1" t="n">
-        <v>-6.081511110300375</v>
+        <v>-6.081511110087198</v>
       </c>
       <c r="D1" t="n">
         <v>0</v>
@@ -433,7 +433,7 @@
         <v>0</v>
       </c>
       <c r="F1" t="n">
-        <v>-0.12104788088997</v>
+        <v>-0.1210478808938077</v>
       </c>
       <c r="G1" t="n">
         <v>0</v>
@@ -442,16 +442,16 @@
         <v>0</v>
       </c>
       <c r="I1" t="n">
-        <v>-0.01668018157227462</v>
+        <v>-0.01668018157168992</v>
       </c>
       <c r="J1" t="n">
-        <v>-2.426468519778474e-24</v>
+        <v>-2.426468519608362e-24</v>
       </c>
       <c r="K1" t="n">
-        <v>-3.592610289694346e-07</v>
+        <v>-3.471516989601026e-07</v>
       </c>
       <c r="L1" t="n">
-        <v>-0.03915535047898094</v>
+        <v>-0.03769560847297628</v>
       </c>
       <c r="M1" t="n">
         <v>0</v>
@@ -460,7 +460,7 @@
         <v>0</v>
       </c>
       <c r="O1" t="n">
-        <v>1.98207483139629e-06</v>
+        <v>1.741562082144905e-06</v>
       </c>
       <c r="P1" t="n">
         <v>0</v>
@@ -469,16 +469,16 @@
         <v>0</v>
       </c>
       <c r="R1" t="n">
-        <v>0.1697869266638625</v>
+        <v>0.1682154757461185</v>
       </c>
       <c r="S1" t="n">
-        <v>-0.0001184549818377263</v>
+        <v>-0.0001179903936238039</v>
       </c>
       <c r="T1" t="n">
-        <v>-0.960924326667485</v>
+        <v>-0.9261160629659022</v>
       </c>
       <c r="U1" t="n">
-        <v>-1.949764334872834</v>
+        <v>-1.942479411279234</v>
       </c>
       <c r="V1" t="n">
         <v>0</v>
@@ -487,7 +487,7 @@
         <v>0</v>
       </c>
       <c r="X1" t="n">
-        <v>1.910852243809187</v>
+        <v>1.890483898956321</v>
       </c>
       <c r="Y1" t="n">
         <v>0</v>
@@ -496,18 +496,18 @@
         <v>0</v>
       </c>
       <c r="AA1" t="n">
-        <v>3.452459828511729</v>
+        <v>3.451997455899638</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>-5.989904541595686</v>
+        <v>-5.98990454337081</v>
       </c>
       <c r="B2" t="n">
-        <v>-15.09305398356022</v>
+        <v>-15.09301851593749</v>
       </c>
       <c r="C2" t="n">
-        <v>-10.51368000577826</v>
+        <v>-10.5126689446311</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -516,7 +516,7 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.8258932807273304</v>
+        <v>-0.8257826657668221</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -525,16 +525,16 @@
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.547886632726138</v>
+        <v>-0.5452322485065547</v>
       </c>
       <c r="J2" t="n">
-        <v>-3.592610289694346e-07</v>
+        <v>-3.471516989601026e-07</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.001270845815519132</v>
+        <v>-0.001270845562090111</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.203558736265448</v>
+        <v>-0.1850265323141821</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
@@ -543,7 +543,7 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>0.003612406640467392</v>
+        <v>0.003612071951874159</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
@@ -552,16 +552,16 @@
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>0.9025657013005344</v>
+        <v>0.6612681434687793</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.2696191341859307</v>
+        <v>-0.2480778465831321</v>
       </c>
       <c r="T2" t="n">
-        <v>-3.242282060338878</v>
+        <v>-2.857346177413353</v>
       </c>
       <c r="U2" t="n">
-        <v>-4.35168195203471</v>
+        <v>-4.231178698510417</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -570,7 +570,7 @@
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>5.733628420397111</v>
+        <v>4.511952828895731</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -579,18 +579,18 @@
         <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>6.528113455778432</v>
+        <v>6.428167563324695</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>-6.081511110300375</v>
+        <v>-6.081511110087198</v>
       </c>
       <c r="B3" t="n">
-        <v>-10.51368000577826</v>
+        <v>-10.5126689446311</v>
       </c>
       <c r="C3" t="n">
-        <v>-11.19543203181506</v>
+        <v>-11.13323389361567</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -599,7 +599,7 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.8034310771642938</v>
+        <v>-0.8001235669443573</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -608,16 +608,16 @@
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.601989910290022</v>
+        <v>-1.411604336325851</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.03915535047898094</v>
+        <v>-0.03769560847297628</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.203558736265448</v>
+        <v>-0.1850265323141821</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.9163285776886917</v>
+        <v>-0.9039480547357948</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
@@ -626,7 +626,7 @@
         <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>0.305976694458814</v>
+        <v>0.2502499924391978</v>
       </c>
       <c r="P3" t="n">
         <v>0</v>
@@ -635,16 +635,16 @@
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>2.255940037426353</v>
+        <v>2.059286915458161</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.86432635735938</v>
+        <v>-1.839182303051824</v>
       </c>
       <c r="T3" t="n">
-        <v>-5.602661732877737</v>
+        <v>-5.131745771399457</v>
       </c>
       <c r="U3" t="n">
-        <v>-7.392371699200923</v>
+        <v>-6.525842856834254</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -653,7 +653,7 @@
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>5.430946795093327</v>
+        <v>4.609557090653587</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
@@ -662,7 +662,7 @@
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>7.440401042558289</v>
+        <v>6.946402356924814</v>
       </c>
     </row>
     <row r="4">
@@ -676,7 +676,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>-16.08517634459811</v>
+        <v>-16.08303407549988</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -685,7 +685,7 @@
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>-5.980207741173712</v>
+        <v>-5.946810732575603</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -703,7 +703,7 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.0004160610460695013</v>
+        <v>-0.0004156470249324775</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
@@ -712,7 +712,7 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.1345919856254981</v>
+        <v>-0.09193164665067313</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -730,7 +730,7 @@
         <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.525186960906869</v>
+        <v>-1.354280886817311</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
@@ -739,7 +739,7 @@
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>-2.005151521563739</v>
+        <v>-1.949023002288205</v>
       </c>
       <c r="Z4" t="n">
         <v>0</v>
@@ -762,7 +762,7 @@
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>-16.08517634459811</v>
+        <v>-16.08303407549988</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
@@ -771,7 +771,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>-5.980207741173712</v>
+        <v>-5.946810732575603</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -789,7 +789,7 @@
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.0004160610460695013</v>
+        <v>-0.0004156470249324775</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -798,7 +798,7 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.1345919856254981</v>
+        <v>-0.09193164665067313</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -816,7 +816,7 @@
         <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>-1.525186960906869</v>
+        <v>-1.354280886817311</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -825,7 +825,7 @@
         <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>-2.005151521563739</v>
+        <v>-1.949023002288205</v>
       </c>
       <c r="AA5" t="n">
         <v>0</v>
@@ -833,13 +833,13 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>-0.12104788088997</v>
+        <v>-0.1210478808938077</v>
       </c>
       <c r="B6" t="n">
-        <v>-0.8258932807273304</v>
+        <v>-0.8257826657668221</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.8034310771642938</v>
+        <v>-0.8001235669443573</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -848,7 +848,7 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>-16.43024915310252</v>
+        <v>-16.42775921451895</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -857,16 +857,16 @@
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>-6.335232207286668</v>
+        <v>-6.292998126727282</v>
       </c>
       <c r="J6" t="n">
-        <v>-1.98207483139629e-06</v>
+        <v>-1.741562082144905e-06</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.003612406640467392</v>
+        <v>-0.003612071951874159</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.305976694458814</v>
+        <v>-0.2502499924391978</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -875,7 +875,7 @@
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>0.009842293884927182</v>
+        <v>0.009833401477644903</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
@@ -884,16 +884,16 @@
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.255939547804513</v>
+        <v>0.7995752521759887</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.7201543061610678</v>
+        <v>-0.6004552024193071</v>
       </c>
       <c r="T6" t="n">
-        <v>-3.57741404376198</v>
+        <v>-3.244455132987019</v>
       </c>
       <c r="U6" t="n">
-        <v>-2.238214641881846</v>
+        <v>-2.233642766879676</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -902,7 +902,7 @@
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>4.89278018900788</v>
+        <v>4.372236174167035</v>
       </c>
       <c r="Y6" t="n">
         <v>0</v>
@@ -911,7 +911,7 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.38357932655242</v>
+        <v>1.324838401303343</v>
       </c>
     </row>
     <row r="7">
@@ -925,7 +925,7 @@
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>-5.980207741173712</v>
+        <v>-5.946810732575603</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -934,7 +934,7 @@
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>-9.26064139200119</v>
+        <v>-8.390298416680842</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -952,7 +952,7 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.1345919856254981</v>
+        <v>-0.09193164665067313</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
@@ -961,7 +961,7 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.8647345469824654</v>
+        <v>-0.6917775592374027</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -979,7 +979,7 @@
         <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>-4.19445046949212</v>
+        <v>-3.30571661330901</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
@@ -988,7 +988,7 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>-4.875462036164374</v>
+        <v>-4.757336710817257</v>
       </c>
       <c r="Z7" t="n">
         <v>0</v>
@@ -1011,7 +1011,7 @@
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>-5.980207741173712</v>
+        <v>-5.946810732575603</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -1020,7 +1020,7 @@
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>-9.26064139200119</v>
+        <v>-8.390298416680842</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -1038,7 +1038,7 @@
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.1345919856254981</v>
+        <v>-0.09193164665067313</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1047,7 +1047,7 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.8647345469824654</v>
+        <v>-0.6917775592374027</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -1065,7 +1065,7 @@
         <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>-4.19445046949212</v>
+        <v>-3.30571661330901</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
@@ -1074,7 +1074,7 @@
         <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>-4.875462036164374</v>
+        <v>-4.757336710817257</v>
       </c>
       <c r="AA8" t="n">
         <v>0</v>
@@ -1082,13 +1082,13 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>-0.01668018157227462</v>
+        <v>-0.01668018157168992</v>
       </c>
       <c r="B9" t="n">
-        <v>-0.547886632726138</v>
+        <v>-0.5452322485065547</v>
       </c>
       <c r="C9" t="n">
-        <v>-1.601989910290022</v>
+        <v>-1.411604336325851</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
@@ -1097,7 +1097,7 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>-6.335232207286668</v>
+        <v>-6.292998126727282</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -1106,16 +1106,16 @@
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>-11.10657339260635</v>
+        <v>-9.613918033536988</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.1697869266638625</v>
+        <v>-0.1682154757461185</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.9025657013005346</v>
+        <v>-0.6612681434687794</v>
       </c>
       <c r="L9" t="n">
-        <v>-2.255940037426353</v>
+        <v>-2.059286915458161</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -1124,7 +1124,7 @@
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>1.255939547804513</v>
+        <v>0.7995752521759887</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
@@ -1133,16 +1133,16 @@
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>4.623385533431726</v>
+        <v>3.808343199401846</v>
       </c>
       <c r="S9" t="n">
-        <v>-4.03478178682664</v>
+        <v>-4.027383785973442</v>
       </c>
       <c r="T9" t="n">
-        <v>-8.765813080614308</v>
+        <v>-7.520035118929481</v>
       </c>
       <c r="U9" t="n">
-        <v>-6.928029018168453</v>
+        <v>-6.078942321179602</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1151,7 +1151,7 @@
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>3.968705619986379</v>
+        <v>3.199061981262096</v>
       </c>
       <c r="Y9" t="n">
         <v>0</v>
@@ -1160,18 +1160,18 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.3618183111927854</v>
+        <v>0.5927228112360096</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>-2.426468519778474e-24</v>
+        <v>-2.426468519608362e-24</v>
       </c>
       <c r="B10" t="n">
-        <v>-3.592610289694346e-07</v>
+        <v>-3.471516989601026e-07</v>
       </c>
       <c r="C10" t="n">
-        <v>-0.03915535047898094</v>
+        <v>-0.03769560847297628</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
@@ -1180,7 +1180,7 @@
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.98207483139629e-06</v>
+        <v>-1.741562082144905e-06</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -1189,16 +1189,16 @@
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.1697869266638625</v>
+        <v>-0.1682154757461185</v>
       </c>
       <c r="J10" t="n">
-        <v>-66.0430810802811</v>
+        <v>-66.04308107565103</v>
       </c>
       <c r="K10" t="n">
-        <v>-5.989904541595686</v>
+        <v>-5.98990454337081</v>
       </c>
       <c r="L10" t="n">
-        <v>-6.081511110300375</v>
+        <v>-6.081511110087198</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -1207,7 +1207,7 @@
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>0.12104788088997</v>
+        <v>0.1210478808938077</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
@@ -1216,16 +1216,16 @@
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0.01668018157227462</v>
+        <v>0.01668018157168992</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.0001184549818377263</v>
+        <v>-0.0001179903936238039</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.960924326667485</v>
+        <v>-0.9261160629659022</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.949764334872834</v>
+        <v>-1.942479411279234</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1234,7 +1234,7 @@
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.910852243809187</v>
+        <v>-1.890483898956321</v>
       </c>
       <c r="Y10" t="n">
         <v>0</v>
@@ -1243,18 +1243,18 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>-3.452459828511729</v>
+        <v>-3.451997455899638</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>-3.592610289694346e-07</v>
+        <v>-3.471516989601026e-07</v>
       </c>
       <c r="B11" t="n">
-        <v>-0.001270845815519132</v>
+        <v>-0.001270845562090111</v>
       </c>
       <c r="C11" t="n">
-        <v>-0.203558736265448</v>
+        <v>-0.1850265323141821</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
@@ -1263,7 +1263,7 @@
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.003612406640467392</v>
+        <v>-0.003612071951874159</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -1272,16 +1272,16 @@
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.9025657013005346</v>
+        <v>-0.6612681434687794</v>
       </c>
       <c r="J11" t="n">
-        <v>-5.989904541595686</v>
+        <v>-5.98990454337081</v>
       </c>
       <c r="K11" t="n">
-        <v>-15.09305398356022</v>
+        <v>-15.09301851593749</v>
       </c>
       <c r="L11" t="n">
-        <v>-10.51368000577826</v>
+        <v>-10.5126689446311</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -1290,7 +1290,7 @@
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>0.8258932807273304</v>
+        <v>0.8257826657668221</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
@@ -1299,16 +1299,16 @@
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>0.547886632726138</v>
+        <v>0.5452322485065547</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.2696191341859307</v>
+        <v>-0.2480778465831321</v>
       </c>
       <c r="T11" t="n">
-        <v>-3.242282060338878</v>
+        <v>-2.857346177413353</v>
       </c>
       <c r="U11" t="n">
-        <v>-4.35168195203471</v>
+        <v>-4.231178698510417</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1317,7 +1317,7 @@
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-5.733628420397111</v>
+        <v>-4.511952828895731</v>
       </c>
       <c r="Y11" t="n">
         <v>0</v>
@@ -1326,18 +1326,18 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>-6.528113455778432</v>
+        <v>-6.428167563324695</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>-0.03915535047898094</v>
+        <v>-0.03769560847297628</v>
       </c>
       <c r="B12" t="n">
-        <v>-0.203558736265448</v>
+        <v>-0.1850265323141821</v>
       </c>
       <c r="C12" t="n">
-        <v>-0.9163285776886917</v>
+        <v>-0.9039480547357948</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
@@ -1346,7 +1346,7 @@
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.305976694458814</v>
+        <v>-0.2502499924391978</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -1355,16 +1355,16 @@
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>-2.255940037426353</v>
+        <v>-2.059286915458161</v>
       </c>
       <c r="J12" t="n">
-        <v>-6.081511110300375</v>
+        <v>-6.081511110087198</v>
       </c>
       <c r="K12" t="n">
-        <v>-10.51368000577826</v>
+        <v>-10.5126689446311</v>
       </c>
       <c r="L12" t="n">
-        <v>-11.19543203181506</v>
+        <v>-11.13323389361567</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
@@ -1373,7 +1373,7 @@
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>0.8034310771642938</v>
+        <v>0.8001235669443573</v>
       </c>
       <c r="P12" t="n">
         <v>0</v>
@@ -1382,16 +1382,16 @@
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.601989910290022</v>
+        <v>1.411604336325851</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.86432635735938</v>
+        <v>-1.839182303051824</v>
       </c>
       <c r="T12" t="n">
-        <v>-5.602661732877737</v>
+        <v>-5.131745771399457</v>
       </c>
       <c r="U12" t="n">
-        <v>-7.392371699200923</v>
+        <v>-6.525842856834254</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1400,7 +1400,7 @@
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-5.430946795093327</v>
+        <v>-4.609557090653587</v>
       </c>
       <c r="Y12" t="n">
         <v>0</v>
@@ -1409,7 +1409,7 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>-7.440401042558289</v>
+        <v>-6.946402356924814</v>
       </c>
     </row>
     <row r="13">
@@ -1423,7 +1423,7 @@
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.0004160610460695013</v>
+        <v>-0.0004156470249324775</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -1432,7 +1432,7 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.1345919856254981</v>
+        <v>-0.09193164665067313</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -1450,7 +1450,7 @@
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>-16.08517634459811</v>
+        <v>-16.08303407549988</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -1459,7 +1459,7 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>-5.980207741173712</v>
+        <v>-5.946810732575603</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -1477,7 +1477,7 @@
         <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>-1.525186960906869</v>
+        <v>-1.354280886817311</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
@@ -1486,7 +1486,7 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>-2.005151521563739</v>
+        <v>-1.949023002288205</v>
       </c>
       <c r="Z13" t="n">
         <v>0</v>
@@ -1509,7 +1509,7 @@
         <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.0004160610460695013</v>
+        <v>-0.0004156470249324775</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
@@ -1518,7 +1518,7 @@
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.1345919856254981</v>
+        <v>-0.09193164665067313</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -1536,7 +1536,7 @@
         <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>-16.08517634459811</v>
+        <v>-16.08303407549988</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -1545,7 +1545,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>-5.980207741173712</v>
+        <v>-5.946810732575603</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -1563,7 +1563,7 @@
         <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>-1.525186960906869</v>
+        <v>-1.354280886817311</v>
       </c>
       <c r="X14" t="n">
         <v>0</v>
@@ -1572,7 +1572,7 @@
         <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>-2.005151521563739</v>
+        <v>-1.949023002288205</v>
       </c>
       <c r="AA14" t="n">
         <v>0</v>
@@ -1580,13 +1580,13 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>1.98207483139629e-06</v>
+        <v>1.741562082144905e-06</v>
       </c>
       <c r="B15" t="n">
-        <v>0.003612406640467392</v>
+        <v>0.003612071951874159</v>
       </c>
       <c r="C15" t="n">
-        <v>0.305976694458814</v>
+        <v>0.2502499924391978</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
@@ -1595,7 +1595,7 @@
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>0.009842293884927182</v>
+        <v>0.009833401477644903</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -1604,16 +1604,16 @@
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>1.255939547804513</v>
+        <v>0.7995752521759887</v>
       </c>
       <c r="J15" t="n">
-        <v>0.12104788088997</v>
+        <v>0.1210478808938077</v>
       </c>
       <c r="K15" t="n">
-        <v>0.8258932807273304</v>
+        <v>0.8257826657668221</v>
       </c>
       <c r="L15" t="n">
-        <v>0.8034310771642938</v>
+        <v>0.8001235669443573</v>
       </c>
       <c r="M15" t="n">
         <v>0</v>
@@ -1622,7 +1622,7 @@
         <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>-16.43024915310252</v>
+        <v>-16.42775921451895</v>
       </c>
       <c r="P15" t="n">
         <v>0</v>
@@ -1631,16 +1631,16 @@
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>-6.335232207286668</v>
+        <v>-6.292998126727282</v>
       </c>
       <c r="S15" t="n">
-        <v>0.7201543061610678</v>
+        <v>0.6004552024193071</v>
       </c>
       <c r="T15" t="n">
-        <v>3.57741404376198</v>
+        <v>3.244455132987019</v>
       </c>
       <c r="U15" t="n">
-        <v>2.238214641881846</v>
+        <v>2.233642766879676</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1649,7 +1649,7 @@
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>4.89278018900788</v>
+        <v>4.372236174167035</v>
       </c>
       <c r="Y15" t="n">
         <v>0</v>
@@ -1658,7 +1658,7 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.38357932655242</v>
+        <v>1.324838401303343</v>
       </c>
     </row>
     <row r="16">
@@ -1672,7 +1672,7 @@
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.1345919856254981</v>
+        <v>-0.09193164665067313</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -1681,7 +1681,7 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.8647345469824654</v>
+        <v>-0.6917775592374027</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1699,7 +1699,7 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>-5.980207741173712</v>
+        <v>-5.946810732575603</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -1708,7 +1708,7 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>-9.26064139200119</v>
+        <v>-8.390298416680842</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -1726,7 +1726,7 @@
         <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>-4.19445046949212</v>
+        <v>-3.30571661330901</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
@@ -1735,7 +1735,7 @@
         <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>-4.875462036164374</v>
+        <v>-4.757336710817257</v>
       </c>
       <c r="Z16" t="n">
         <v>0</v>
@@ -1758,7 +1758,7 @@
         <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.1345919856254981</v>
+        <v>-0.09193164665067313</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
@@ -1767,7 +1767,7 @@
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.8647345469824654</v>
+        <v>-0.6917775592374027</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -1785,7 +1785,7 @@
         <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>-5.980207741173712</v>
+        <v>-5.946810732575603</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -1794,7 +1794,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>-9.26064139200119</v>
+        <v>-8.390298416680842</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -1812,7 +1812,7 @@
         <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>-4.19445046949212</v>
+        <v>-3.30571661330901</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
@@ -1821,7 +1821,7 @@
         <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>-4.875462036164374</v>
+        <v>-4.757336710817257</v>
       </c>
       <c r="AA17" t="n">
         <v>0</v>
@@ -1829,13 +1829,13 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>0.1697869266638625</v>
+        <v>0.1682154757461185</v>
       </c>
       <c r="B18" t="n">
-        <v>0.9025657013005344</v>
+        <v>0.6612681434687793</v>
       </c>
       <c r="C18" t="n">
-        <v>2.255940037426353</v>
+        <v>2.059286915458161</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
@@ -1844,7 +1844,7 @@
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>1.255939547804513</v>
+        <v>0.7995752521759887</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -1853,16 +1853,16 @@
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>4.623385533431726</v>
+        <v>3.808343199401846</v>
       </c>
       <c r="J18" t="n">
-        <v>0.01668018157227462</v>
+        <v>0.01668018157168992</v>
       </c>
       <c r="K18" t="n">
-        <v>0.547886632726138</v>
+        <v>0.5452322485065547</v>
       </c>
       <c r="L18" t="n">
-        <v>1.601989910290022</v>
+        <v>1.411604336325851</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -1871,7 +1871,7 @@
         <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>-6.335232207286668</v>
+        <v>-6.292998126727282</v>
       </c>
       <c r="P18" t="n">
         <v>0</v>
@@ -1880,16 +1880,16 @@
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>-11.10657339260635</v>
+        <v>-9.613918033536988</v>
       </c>
       <c r="S18" t="n">
-        <v>4.03478178682664</v>
+        <v>4.027383785973442</v>
       </c>
       <c r="T18" t="n">
-        <v>8.765813080614308</v>
+        <v>7.520035118929481</v>
       </c>
       <c r="U18" t="n">
-        <v>6.928029018168453</v>
+        <v>6.078942321179602</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1898,7 +1898,7 @@
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>3.968705619986379</v>
+        <v>3.199061981262096</v>
       </c>
       <c r="Y18" t="n">
         <v>0</v>
@@ -1907,18 +1907,18 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>0.3618183111927854</v>
+        <v>0.5927228112360096</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>-0.0001184549818377263</v>
+        <v>-0.0001179903936238039</v>
       </c>
       <c r="B19" t="n">
-        <v>-0.2696191341859307</v>
+        <v>-0.2480778465831321</v>
       </c>
       <c r="C19" t="n">
-        <v>-1.86432635735938</v>
+        <v>-1.839182303051824</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
@@ -1927,7 +1927,7 @@
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.7201543061610678</v>
+        <v>-0.6004552024193071</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -1936,16 +1936,16 @@
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>-4.03478178682664</v>
+        <v>-4.027383785973442</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.0001184549818377263</v>
+        <v>-0.0001179903936238039</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.2696191341859307</v>
+        <v>-0.2480778465831321</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.86432635735938</v>
+        <v>-1.839182303051824</v>
       </c>
       <c r="M19" t="n">
         <v>0</v>
@@ -1954,7 +1954,7 @@
         <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>0.7201543061610678</v>
+        <v>0.6004552024193071</v>
       </c>
       <c r="P19" t="n">
         <v>0</v>
@@ -1963,16 +1963,16 @@
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>4.03478178682664</v>
+        <v>4.027383785973442</v>
       </c>
       <c r="S19" t="n">
-        <v>-41.451741958451</v>
+        <v>-41.45174196517276</v>
       </c>
       <c r="T19" t="n">
-        <v>-4.011778218356612</v>
+        <v>-4.011778218080271</v>
       </c>
       <c r="U19" t="n">
-        <v>-4.597806343053742</v>
+        <v>-4.597806343426529</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1995,13 +1995,13 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>-0.960924326667485</v>
+        <v>-0.9261160629659022</v>
       </c>
       <c r="B20" t="n">
-        <v>-3.242282060338878</v>
+        <v>-2.857346177413353</v>
       </c>
       <c r="C20" t="n">
-        <v>-5.602661732877737</v>
+        <v>-5.131745771399457</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
@@ -2010,7 +2010,7 @@
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>-3.57741404376198</v>
+        <v>-3.244455132987019</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -2019,16 +2019,16 @@
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>-8.765813080614308</v>
+        <v>-7.520035118929481</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.960924326667485</v>
+        <v>-0.9261160629659022</v>
       </c>
       <c r="K20" t="n">
-        <v>-3.242282060338878</v>
+        <v>-2.857346177413353</v>
       </c>
       <c r="L20" t="n">
-        <v>-5.602661732877737</v>
+        <v>-5.131745771399457</v>
       </c>
       <c r="M20" t="n">
         <v>0</v>
@@ -2037,7 +2037,7 @@
         <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>3.57741404376198</v>
+        <v>3.244455132987019</v>
       </c>
       <c r="P20" t="n">
         <v>0</v>
@@ -2046,16 +2046,16 @@
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>8.765813080614308</v>
+        <v>7.520035118929481</v>
       </c>
       <c r="S20" t="n">
-        <v>-4.011778218356612</v>
+        <v>-4.011778218080271</v>
       </c>
       <c r="T20" t="n">
-        <v>-13.02045233736774</v>
+        <v>-13.00881947978265</v>
       </c>
       <c r="U20" t="n">
-        <v>-10.06466693961846</v>
+        <v>-10.00675332709381</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2078,13 +2078,13 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>-1.949764334872834</v>
+        <v>-1.942479411279234</v>
       </c>
       <c r="B21" t="n">
-        <v>-4.35168195203471</v>
+        <v>-4.231178698510417</v>
       </c>
       <c r="C21" t="n">
-        <v>-7.392371699200923</v>
+        <v>-6.525842856834254</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.238214641881846</v>
+        <v>-2.233642766879676</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -2102,16 +2102,16 @@
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>-6.928029018168453</v>
+        <v>-6.078942321179602</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.949764334872834</v>
+        <v>-1.942479411279234</v>
       </c>
       <c r="K21" t="n">
-        <v>-4.35168195203471</v>
+        <v>-4.231178698510417</v>
       </c>
       <c r="L21" t="n">
-        <v>-7.392371699200923</v>
+        <v>-6.525842856834254</v>
       </c>
       <c r="M21" t="n">
         <v>0</v>
@@ -2120,7 +2120,7 @@
         <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>2.238214641881846</v>
+        <v>2.233642766879676</v>
       </c>
       <c r="P21" t="n">
         <v>0</v>
@@ -2129,16 +2129,16 @@
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>6.928029018168453</v>
+        <v>6.078942321179602</v>
       </c>
       <c r="S21" t="n">
-        <v>-4.597806343053742</v>
+        <v>-4.597806343426529</v>
       </c>
       <c r="T21" t="n">
-        <v>-10.06466693961846</v>
+        <v>-10.00675332709381</v>
       </c>
       <c r="U21" t="n">
-        <v>-11.23175690046761</v>
+        <v>-10.70815584082509</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
         <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.525186960906869</v>
+        <v>-1.354280886817311</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -2179,7 +2179,7 @@
         <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>-4.19445046949212</v>
+        <v>-3.30571661330901</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
@@ -2197,7 +2197,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.525186960906869</v>
+        <v>-1.354280886817311</v>
       </c>
       <c r="N22" t="n">
         <v>0</v>
@@ -2206,7 +2206,7 @@
         <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>-4.19445046949212</v>
+        <v>-3.30571661330901</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
@@ -2224,7 +2224,7 @@
         <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>-13.27217972940464</v>
+        <v>-13.040512775672</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
@@ -2233,7 +2233,7 @@
         <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>-6.71642884283359</v>
+        <v>-5.998964691456903</v>
       </c>
       <c r="Z22" t="n">
         <v>0</v>
@@ -2256,7 +2256,7 @@
         <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.525186960906869</v>
+        <v>-1.354280886817311</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
@@ -2265,7 +2265,7 @@
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>-4.19445046949212</v>
+        <v>-3.30571661330901</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
@@ -2283,7 +2283,7 @@
         <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.525186960906869</v>
+        <v>-1.354280886817311</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -2292,7 +2292,7 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>-4.19445046949212</v>
+        <v>-3.30571661330901</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -2310,7 +2310,7 @@
         <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>-13.27217972940464</v>
+        <v>-13.040512775672</v>
       </c>
       <c r="X23" t="n">
         <v>0</v>
@@ -2319,7 +2319,7 @@
         <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>-6.71642884283359</v>
+        <v>-5.998964691456903</v>
       </c>
       <c r="AA23" t="n">
         <v>0</v>
@@ -2327,13 +2327,13 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>1.910852243809187</v>
+        <v>1.890483898956321</v>
       </c>
       <c r="B24" t="n">
-        <v>5.733628420397111</v>
+        <v>4.511952828895731</v>
       </c>
       <c r="C24" t="n">
-        <v>5.430946795093327</v>
+        <v>4.609557090653587</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
@@ -2342,7 +2342,7 @@
         <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>4.89278018900788</v>
+        <v>4.372236174167035</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -2351,16 +2351,16 @@
         <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>3.968705619986379</v>
+        <v>3.199061981262096</v>
       </c>
       <c r="J24" t="n">
-        <v>-1.910852243809187</v>
+        <v>-1.890483898956321</v>
       </c>
       <c r="K24" t="n">
-        <v>-5.733628420397111</v>
+        <v>-4.511952828895731</v>
       </c>
       <c r="L24" t="n">
-        <v>-5.430946795093327</v>
+        <v>-4.609557090653587</v>
       </c>
       <c r="M24" t="n">
         <v>0</v>
@@ -2369,7 +2369,7 @@
         <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>4.89278018900788</v>
+        <v>4.372236174167035</v>
       </c>
       <c r="P24" t="n">
         <v>0</v>
@@ -2378,7 +2378,7 @@
         <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>3.968705619986379</v>
+        <v>3.199061981262096</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -2396,7 +2396,7 @@
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-14.78485385221668</v>
+        <v>-14.47983952341933</v>
       </c>
       <c r="Y24" t="n">
         <v>0</v>
@@ -2405,7 +2405,7 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>-8.380661085124931</v>
+        <v>-7.29563201096085</v>
       </c>
     </row>
     <row r="25">
@@ -2419,7 +2419,7 @@
         <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>-2.005151521563739</v>
+        <v>-1.949023002288205</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
@@ -2428,7 +2428,7 @@
         <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>-4.875462036164374</v>
+        <v>-4.757336710817257</v>
       </c>
       <c r="H25" t="n">
         <v>0</v>
@@ -2446,7 +2446,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>-2.005151521563739</v>
+        <v>-1.949023002288205</v>
       </c>
       <c r="N25" t="n">
         <v>0</v>
@@ -2455,7 +2455,7 @@
         <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>-4.875462036164374</v>
+        <v>-4.757336710817257</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -2473,7 +2473,7 @@
         <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>-6.71642884283359</v>
+        <v>-5.998964691456903</v>
       </c>
       <c r="W25" t="n">
         <v>0</v>
@@ -2482,7 +2482,7 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>-11.32885260119357</v>
+        <v>-7.946993355247448</v>
       </c>
       <c r="Z25" t="n">
         <v>0</v>
@@ -2505,7 +2505,7 @@
         <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>-2.005151521563739</v>
+        <v>-1.949023002288205</v>
       </c>
       <c r="F26" t="n">
         <v>0</v>
@@ -2514,7 +2514,7 @@
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>-4.875462036164374</v>
+        <v>-4.757336710817257</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
@@ -2532,7 +2532,7 @@
         <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>-2.005151521563739</v>
+        <v>-1.949023002288205</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -2541,7 +2541,7 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>-4.875462036164374</v>
+        <v>-4.757336710817257</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -2559,7 +2559,7 @@
         <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>-6.71642884283359</v>
+        <v>-5.998964691456903</v>
       </c>
       <c r="X26" t="n">
         <v>0</v>
@@ -2568,7 +2568,7 @@
         <v>0</v>
       </c>
       <c r="Z26" t="n">
-        <v>-11.32885260119357</v>
+        <v>-7.946993355247448</v>
       </c>
       <c r="AA26" t="n">
         <v>0</v>
@@ -2576,13 +2576,13 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>3.452459828511729</v>
+        <v>3.451997455899638</v>
       </c>
       <c r="B27" t="n">
-        <v>6.528113455778432</v>
+        <v>6.428167563324695</v>
       </c>
       <c r="C27" t="n">
-        <v>7.440401042558289</v>
+        <v>6.946402356924814</v>
       </c>
       <c r="D27" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
         <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>1.38357932655242</v>
+        <v>1.324838401303343</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -2600,16 +2600,16 @@
         <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>0.3618183111927854</v>
+        <v>0.5927228112360096</v>
       </c>
       <c r="J27" t="n">
-        <v>-3.452459828511729</v>
+        <v>-3.451997455899638</v>
       </c>
       <c r="K27" t="n">
-        <v>-6.528113455778432</v>
+        <v>-6.428167563324695</v>
       </c>
       <c r="L27" t="n">
-        <v>-7.440401042558289</v>
+        <v>-6.946402356924814</v>
       </c>
       <c r="M27" t="n">
         <v>0</v>
@@ -2618,7 +2618,7 @@
         <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>1.38357932655242</v>
+        <v>1.324838401303343</v>
       </c>
       <c r="P27" t="n">
         <v>0</v>
@@ -2627,7 +2627,7 @@
         <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>0.3618183111927854</v>
+        <v>0.5927228112360096</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -2645,7 +2645,7 @@
         <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>-8.380661085124931</v>
+        <v>-7.29563201096085</v>
       </c>
       <c r="Y27" t="n">
         <v>0</v>
@@ -2654,7 +2654,7 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>-18.13062673804512</v>
+        <v>-10.22523404402575</v>
       </c>
     </row>
   </sheetData>
